--- a/documentation/integrations/DataExchangeSpecification_v1.0.1.xlsx
+++ b/documentation/integrations/DataExchangeSpecification_v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\io\41-19-12-2025\documentation\integrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34936B1C-9F9A-4D28-8B97-039CC5C300E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836D468B-B526-4806-81C9-7446F1F1D7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="417">
   <si>
     <t>Съобщение</t>
   </si>
@@ -646,9 +646,6 @@
     <t>certificateNumber</t>
   </si>
   <si>
-    <t>Номер на сертификат за енергийни характеристики</t>
-  </si>
-  <si>
     <t>ГРАО, МВР</t>
   </si>
   <si>
@@ -1298,6 +1295,18 @@
   </si>
   <si>
     <t>Премахнат е operationId от съобщение E002</t>
+  </si>
+  <si>
+    <t>min=8, max=9, chars=n</t>
+  </si>
+  <si>
+    <t>Номер на сертификат за енергийни характеристики (с премахнати букви)</t>
+  </si>
+  <si>
+    <t>В съобщение E007 е премахнато полето address</t>
+  </si>
+  <si>
+    <t>В съобщение E007 е коригиран формата на полето certificateNumber</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1524,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="92">
+  <borders count="93">
     <border>
       <left/>
       <right/>
@@ -2757,6 +2766,21 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -2775,7 +2799,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3255,6 +3279,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="92" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
@@ -3538,7 +3565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08192E09-6292-4A91-B17D-80DDC8ADAD3E}">
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3551,82 +3578,82 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
@@ -3636,42 +3663,42 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
@@ -3681,37 +3708,47 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" s="176" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>413</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -3946,7 +3983,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="68" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -3963,7 +4000,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="24"/>
@@ -4017,7 +4054,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="156" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B13" s="41" t="s">
         <v>21</v>
@@ -4044,7 +4081,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="156" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>21</v>
@@ -4071,7 +4108,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="85" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B15" s="144" t="s">
         <v>51</v>
@@ -4084,19 +4121,19 @@
       <c r="F15" s="143"/>
       <c r="G15" s="143"/>
       <c r="H15" s="54" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I15" s="143"/>
       <c r="J15" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="K15" s="79" t="s">
         <v>236</v>
-      </c>
-      <c r="K15" s="79" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="69" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B16" s="41" t="s">
         <v>21</v>
@@ -4112,18 +4149,18 @@
       <c r="G16" s="24"/>
       <c r="H16" s="151"/>
       <c r="I16" s="153" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K16" s="64" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="69" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>21</v>
@@ -4132,7 +4169,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -4140,15 +4177,15 @@
       <c r="H17" s="24"/>
       <c r="I17" s="41"/>
       <c r="J17" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="K17" s="68" t="s">
         <v>251</v>
-      </c>
-      <c r="K17" s="68" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="155" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B18" s="53"/>
       <c r="C18" s="53"/>
@@ -4163,7 +4200,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="85" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B19" s="54" t="s">
         <v>51</v>
@@ -4176,19 +4213,19 @@
       <c r="F19" s="54"/>
       <c r="G19" s="142"/>
       <c r="H19" s="54" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I19" s="54"/>
       <c r="J19" s="54" t="s">
+        <v>237</v>
+      </c>
+      <c r="K19" s="79" t="s">
         <v>238</v>
-      </c>
-      <c r="K19" s="79" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="69" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B20" s="41" t="s">
         <v>21</v>
@@ -4204,18 +4241,18 @@
       <c r="G20" s="24"/>
       <c r="H20" s="151"/>
       <c r="I20" s="153" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J20" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="K20" s="64" t="s">
         <v>257</v>
-      </c>
-      <c r="K20" s="64" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="69" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>21</v>
@@ -4224,7 +4261,7 @@
         <v>22</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
@@ -4232,15 +4269,15 @@
       <c r="H21" s="24"/>
       <c r="I21" s="41"/>
       <c r="J21" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K21" s="68" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="155" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B22" s="53"/>
       <c r="C22" s="53"/>
@@ -4498,7 +4535,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -4515,7 +4552,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -4569,7 +4606,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="143" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B13" s="144" t="s">
         <v>21</v>
@@ -4584,7 +4621,7 @@
       <c r="H13" s="143"/>
       <c r="I13" s="143"/>
       <c r="J13" s="54" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K13" s="142" t="s">
         <v>2</v>
@@ -4614,7 +4651,7 @@
         <v>154</v>
       </c>
       <c r="K14" s="61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
@@ -4643,7 +4680,7 @@
         <v>158</v>
       </c>
       <c r="K15" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
@@ -4724,7 +4761,7 @@
         <v>172</v>
       </c>
       <c r="K18" s="61" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
@@ -4751,7 +4788,7 @@
         <v>173</v>
       </c>
       <c r="K19" s="61" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
@@ -4778,7 +4815,7 @@
         <v>174</v>
       </c>
       <c r="K20" s="61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
@@ -4798,7 +4835,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B22" s="43" t="s">
         <v>21</v>
@@ -4813,10 +4850,10 @@
       <c r="H22" s="45"/>
       <c r="I22" s="45"/>
       <c r="J22" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K22" s="75" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
@@ -4874,7 +4911,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="63" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>21</v>
@@ -4886,22 +4923,22 @@
         <v>29</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
       <c r="I25" s="41"/>
       <c r="J25" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K25" s="83" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="63" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B26" s="24" t="s">
         <v>53</v>
@@ -4913,22 +4950,22 @@
         <v>29</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
       <c r="I26" s="41"/>
       <c r="J26" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="K26" s="83" t="s">
         <v>405</v>
-      </c>
-      <c r="K26" s="83" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>21</v>
@@ -4940,22 +4977,22 @@
         <v>29</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F27" s="24"/>
       <c r="G27" s="24"/>
       <c r="H27" s="24"/>
       <c r="I27" s="41"/>
       <c r="J27" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K27" s="83" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B28" s="72"/>
       <c r="C28" s="72"/>
@@ -4970,7 +5007,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>21</v>
@@ -4985,15 +5022,15 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K29" s="86" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>53</v>
@@ -5012,15 +5049,15 @@
       <c r="H30" s="24"/>
       <c r="I30" s="41"/>
       <c r="J30" s="24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K30" s="83" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="157" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B31" s="24" t="s">
         <v>53</v>
@@ -5039,15 +5076,15 @@
       <c r="H31" s="24"/>
       <c r="I31" s="41"/>
       <c r="J31" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K31" s="74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="66" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B32" s="24" t="s">
         <v>53</v>
@@ -5066,15 +5103,15 @@
       <c r="H32" s="24"/>
       <c r="I32" s="41"/>
       <c r="J32" s="52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K32" s="74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B33" s="72"/>
       <c r="C33" s="72"/>
@@ -5332,7 +5369,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -5349,7 +5386,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -5403,7 +5440,7 @@
     </row>
     <row r="13" spans="1:11" s="95" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="168" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>21</v>
@@ -5422,15 +5459,15 @@
       <c r="H13" s="30"/>
       <c r="I13" s="164"/>
       <c r="J13" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="K13" s="169" t="s">
         <v>299</v>
-      </c>
-      <c r="K13" s="169" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="165" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B14" s="41" t="s">
         <v>21</v>
@@ -5444,11 +5481,11 @@
       <c r="E14" s="24"/>
       <c r="F14" s="41"/>
       <c r="G14" s="56" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H14" s="41"/>
       <c r="I14" s="41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J14" s="24" t="s">
         <v>97</v>
@@ -5459,7 +5496,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="165" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>53</v>
@@ -5486,7 +5523,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="85" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" s="144" t="s">
         <v>51</v>
@@ -5499,11 +5536,11 @@
       <c r="F16" s="143"/>
       <c r="G16" s="143"/>
       <c r="H16" s="54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I16" s="143"/>
       <c r="J16" s="54" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K16" s="79" t="s">
         <v>2</v>
@@ -5533,7 +5570,7 @@
         <v>154</v>
       </c>
       <c r="K17" s="68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
@@ -5562,7 +5599,7 @@
         <v>158</v>
       </c>
       <c r="K18" s="68" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
@@ -5643,7 +5680,7 @@
         <v>172</v>
       </c>
       <c r="K21" s="68" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
@@ -5670,7 +5707,7 @@
         <v>173</v>
       </c>
       <c r="K22" s="68" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
@@ -5697,7 +5734,7 @@
         <v>174</v>
       </c>
       <c r="K23" s="68" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
@@ -5717,7 +5754,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B25" s="43" t="s">
         <v>51</v>
@@ -5730,14 +5767,14 @@
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I25" s="45"/>
       <c r="J25" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K25" s="75" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
@@ -5795,7 +5832,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="63" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>21</v>
@@ -5807,22 +5844,22 @@
         <v>29</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
       <c r="I28" s="41"/>
       <c r="J28" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K28" s="83" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="63" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>53</v>
@@ -5834,22 +5871,22 @@
         <v>29</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F29" s="24"/>
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
       <c r="I29" s="41"/>
       <c r="J29" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="K29" s="83" t="s">
         <v>405</v>
-      </c>
-      <c r="K29" s="83" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>21</v>
@@ -5861,22 +5898,22 @@
         <v>29</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F30" s="24"/>
       <c r="G30" s="24"/>
       <c r="H30" s="24"/>
       <c r="I30" s="41"/>
       <c r="J30" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K30" s="83" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B31" s="72"/>
       <c r="C31" s="72"/>
@@ -5891,7 +5928,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>51</v>
@@ -5904,19 +5941,19 @@
       <c r="F32" s="11"/>
       <c r="G32" s="106"/>
       <c r="H32" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I32" s="11"/>
       <c r="J32" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K32" s="86" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B33" s="24" t="s">
         <v>51</v>
@@ -5933,19 +5970,19 @@
       <c r="F33" s="24"/>
       <c r="G33" s="24"/>
       <c r="H33" s="24" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I33" s="41"/>
       <c r="J33" s="24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K33" s="83" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="157" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B34" s="24" t="s">
         <v>51</v>
@@ -5962,19 +5999,19 @@
       <c r="F34" s="24"/>
       <c r="G34" s="24"/>
       <c r="H34" s="24" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I34" s="41"/>
       <c r="J34" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K34" s="74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="66" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B35" s="24" t="s">
         <v>51</v>
@@ -5991,19 +6028,19 @@
       <c r="F35" s="24"/>
       <c r="G35" s="24"/>
       <c r="H35" s="24" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I35" s="41"/>
       <c r="J35" s="52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K35" s="74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B36" s="72"/>
       <c r="C36" s="72"/>
@@ -6018,7 +6055,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="65" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>53</v>
@@ -6028,24 +6065,24 @@
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F37" s="11"/>
       <c r="G37" s="106"/>
       <c r="H37" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I37" s="11"/>
       <c r="J37" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K37" s="86" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B38" s="24" t="s">
         <v>53</v>
@@ -6054,25 +6091,25 @@
         <v>50</v>
       </c>
       <c r="D38" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="E38" s="24" t="s">
         <v>329</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>330</v>
       </c>
       <c r="F38" s="24"/>
       <c r="G38" s="24"/>
       <c r="H38" s="24"/>
       <c r="I38" s="41"/>
       <c r="J38" s="24" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K38" s="77" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="157" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B39" s="24" t="s">
         <v>53</v>
@@ -6081,25 +6118,25 @@
         <v>50</v>
       </c>
       <c r="D39" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="E39" s="24" t="s">
         <v>329</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>330</v>
       </c>
       <c r="F39" s="24"/>
       <c r="G39" s="24"/>
       <c r="H39" s="24"/>
       <c r="I39" s="41"/>
       <c r="J39" s="24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K39" s="77" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A40" s="71" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B40" s="72"/>
       <c r="C40" s="72"/>
@@ -6358,7 +6395,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -6375,7 +6412,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -6429,7 +6466,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>21</v>
@@ -6441,7 +6478,7 @@
         <v>29</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
@@ -6451,12 +6488,12 @@
         <v>195</v>
       </c>
       <c r="K13" s="61" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="24" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>21</v>
@@ -6465,25 +6502,25 @@
         <v>22</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
       <c r="I14" s="41"/>
       <c r="J14" s="55" t="s">
+        <v>374</v>
+      </c>
+      <c r="K14" s="61" t="s">
         <v>375</v>
-      </c>
-      <c r="K14" s="61" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="24" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>21</v>
@@ -6492,25 +6529,25 @@
         <v>22</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
       <c r="H15" s="24"/>
       <c r="I15" s="41"/>
       <c r="J15" s="55" t="s">
+        <v>377</v>
+      </c>
+      <c r="K15" s="61" t="s">
         <v>378</v>
-      </c>
-      <c r="K15" s="61" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="24" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>21</v>
@@ -6526,18 +6563,18 @@
       <c r="G16" s="24"/>
       <c r="H16" s="151"/>
       <c r="I16" s="24" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J16" s="55" t="s">
+        <v>381</v>
+      </c>
+      <c r="K16" s="61" t="s">
         <v>382</v>
-      </c>
-      <c r="K16" s="61" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="24" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>21</v>
@@ -6553,18 +6590,18 @@
       <c r="G17" s="24"/>
       <c r="H17" s="151"/>
       <c r="I17" s="24" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J17" s="55" t="s">
+        <v>383</v>
+      </c>
+      <c r="K17" s="61" t="s">
         <v>384</v>
-      </c>
-      <c r="K17" s="61" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>53</v>
@@ -6583,15 +6620,15 @@
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="55" t="s">
+        <v>385</v>
+      </c>
+      <c r="K18" s="61" t="s">
         <v>386</v>
-      </c>
-      <c r="K18" s="61" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B19" s="43" t="s">
         <v>21</v>
@@ -6606,10 +6643,10 @@
       <c r="H19" s="45"/>
       <c r="I19" s="45"/>
       <c r="J19" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K19" s="75" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
@@ -6667,7 +6704,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="63" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>21</v>
@@ -6679,22 +6716,22 @@
         <v>29</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
       <c r="I22" s="41"/>
       <c r="J22" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K22" s="83" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="63" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>53</v>
@@ -6706,22 +6743,22 @@
         <v>29</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
       <c r="I23" s="41"/>
       <c r="J23" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="K23" s="83" t="s">
         <v>405</v>
-      </c>
-      <c r="K23" s="83" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>21</v>
@@ -6733,22 +6770,22 @@
         <v>29</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
       <c r="I24" s="41"/>
       <c r="J24" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K24" s="83" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B25" s="72"/>
       <c r="C25" s="72"/>
@@ -6763,7 +6800,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>21</v>
@@ -6778,15 +6815,15 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K26" s="86" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>53</v>
@@ -6805,15 +6842,15 @@
       <c r="H27" s="24"/>
       <c r="I27" s="41"/>
       <c r="J27" s="24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K27" s="83" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="157" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>53</v>
@@ -6832,15 +6869,15 @@
       <c r="H28" s="24"/>
       <c r="I28" s="41"/>
       <c r="J28" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K28" s="74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="66" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>53</v>
@@ -6859,15 +6896,15 @@
       <c r="H29" s="24"/>
       <c r="I29" s="41"/>
       <c r="J29" s="52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K29" s="74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B30" s="72"/>
       <c r="C30" s="72"/>
@@ -7127,7 +7164,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -7144,7 +7181,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -7200,7 +7237,7 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>21</v>
@@ -7212,7 +7249,7 @@
         <v>29</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
@@ -7222,12 +7259,12 @@
         <v>195</v>
       </c>
       <c r="K13" s="61" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>21</v>
@@ -7242,18 +7279,18 @@
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="I14" s="24" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J14" s="55" t="s">
+        <v>381</v>
+      </c>
+      <c r="K14" s="61" t="s">
         <v>382</v>
-      </c>
-      <c r="K14" s="61" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="165" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B15" s="41" t="s">
         <v>21</v>
@@ -7267,11 +7304,11 @@
       <c r="E15" s="51"/>
       <c r="F15" s="41"/>
       <c r="G15" s="56" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H15" s="41"/>
       <c r="I15" s="41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J15" s="24" t="s">
         <v>97</v>
@@ -7282,7 +7319,7 @@
     </row>
     <row r="16" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A16" s="165" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>53</v>
@@ -7551,7 +7588,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -7568,7 +7605,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -7622,7 +7659,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="65" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B13" s="43" t="s">
         <v>21</v>
@@ -7637,10 +7674,10 @@
       <c r="H13" s="45"/>
       <c r="I13" s="45"/>
       <c r="J13" s="54" t="s">
+        <v>393</v>
+      </c>
+      <c r="K13" s="175" t="s">
         <v>394</v>
-      </c>
-      <c r="K13" s="175" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
@@ -7698,7 +7735,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="63" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>21</v>
@@ -7710,22 +7747,22 @@
         <v>29</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="41"/>
       <c r="J16" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K16" s="83" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="63" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>53</v>
@@ -7737,22 +7774,22 @@
         <v>29</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="I17" s="41"/>
       <c r="J17" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="K17" s="83" t="s">
         <v>405</v>
-      </c>
-      <c r="K17" s="83" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>21</v>
@@ -7764,22 +7801,22 @@
         <v>29</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K18" s="83" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B19" s="72"/>
       <c r="C19" s="72"/>
@@ -7794,7 +7831,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>21</v>
@@ -7809,15 +7846,15 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K20" s="86" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>53</v>
@@ -7836,15 +7873,15 @@
       <c r="H21" s="24"/>
       <c r="I21" s="41"/>
       <c r="J21" s="24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K21" s="83" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="157" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>53</v>
@@ -7863,15 +7900,15 @@
       <c r="H22" s="24"/>
       <c r="I22" s="41"/>
       <c r="J22" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K22" s="74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="66" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>53</v>
@@ -7890,15 +7927,15 @@
       <c r="H23" s="24"/>
       <c r="I23" s="41"/>
       <c r="J23" s="52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K23" s="74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B24" s="72"/>
       <c r="C24" s="72"/>
@@ -8157,7 +8194,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -8174,7 +8211,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -8230,7 +8267,7 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="165" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B13" s="41" t="s">
         <v>21</v>
@@ -8244,11 +8281,11 @@
       <c r="E13" s="51"/>
       <c r="F13" s="41"/>
       <c r="G13" s="56" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H13" s="41"/>
       <c r="I13" s="41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>97</v>
@@ -8259,7 +8296,7 @@
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="165" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>53</v>
@@ -8286,7 +8323,7 @@
     </row>
     <row r="15" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>21</v>
@@ -8301,15 +8338,15 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K15" s="86" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A16" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>53</v>
@@ -8328,15 +8365,15 @@
       <c r="H16" s="24"/>
       <c r="I16" s="41"/>
       <c r="J16" s="24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K16" s="83" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A17" s="157" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>53</v>
@@ -8355,15 +8392,15 @@
       <c r="H17" s="24"/>
       <c r="I17" s="41"/>
       <c r="J17" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K17" s="74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A18" s="66" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>53</v>
@@ -8382,15 +8419,15 @@
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K18" s="74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="17" customFormat="1" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B19" s="72"/>
       <c r="C19" s="72"/>
@@ -8647,7 +8684,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -8664,7 +8701,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -8718,7 +8755,7 @@
     </row>
     <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="31" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>21</v>
@@ -8737,15 +8774,15 @@
       <c r="H13" s="30"/>
       <c r="I13" s="164"/>
       <c r="J13" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="K13" s="98" t="s">
         <v>299</v>
-      </c>
-      <c r="K13" s="98" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A14" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>21</v>
@@ -8757,22 +8794,22 @@
         <v>43</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
       <c r="I14" s="34"/>
       <c r="J14" s="34" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A15" s="33" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>51</v>
@@ -8784,19 +8821,19 @@
         <v>43</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34"/>
       <c r="H15" s="34" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I15" s="34"/>
       <c r="J15" s="34" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -9048,7 +9085,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -9065,7 +9102,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -9331,7 +9368,7 @@
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="123"/>
       <c r="B5" s="124" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -9351,135 +9388,135 @@
     <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="123"/>
       <c r="B8" s="124" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="125" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="120" t="s">
         <v>211</v>
-      </c>
-      <c r="B9" s="120" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="121"/>
       <c r="B10" s="122" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="123"/>
       <c r="B11" s="124" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="125" t="s">
+        <v>241</v>
+      </c>
+      <c r="B12" s="120" t="s">
         <v>242</v>
-      </c>
-      <c r="B12" s="120" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="121"/>
       <c r="B13" s="122" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="123"/>
       <c r="B14" s="124" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="125" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B15" s="120" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="121"/>
       <c r="B16" s="122" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="123"/>
       <c r="B17" s="124" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="125" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B18" s="120" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="121"/>
       <c r="B19" s="122" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="123"/>
       <c r="B20" s="124" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="125" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B21" s="120" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="121"/>
       <c r="B22" s="122" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="123"/>
       <c r="B23" s="124" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="125" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B24" s="120" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="121"/>
       <c r="B25" s="122" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="123"/>
       <c r="B26" s="124" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" s="125" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B27" s="170" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -9533,10 +9570,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="126" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B2" s="105" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
@@ -9555,7 +9592,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="126" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B3" s="105" t="s">
         <v>124</v>
@@ -9580,7 +9617,7 @@
         <v>137</v>
       </c>
       <c r="B4" s="105" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C4" s="130"/>
       <c r="D4" s="130"/>
@@ -9591,7 +9628,7 @@
         <v>94</v>
       </c>
       <c r="H4" s="127" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -9599,7 +9636,7 @@
         <v>138</v>
       </c>
       <c r="B5" s="105" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C5" s="130"/>
       <c r="D5" s="130"/>
@@ -9607,7 +9644,7 @@
         <v>139</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H5" s="127" t="s">
         <v>94</v>
@@ -9618,7 +9655,7 @@
         <v>181</v>
       </c>
       <c r="B6" s="105" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="130"/>
       <c r="D6" s="130"/>
@@ -9637,7 +9674,7 @@
         <v>183</v>
       </c>
       <c r="B7" s="105" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C7" s="130"/>
       <c r="D7" s="130"/>
@@ -9653,10 +9690,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="126" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B8" s="105" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C8" s="130"/>
       <c r="D8" s="130"/>
@@ -9667,15 +9704,15 @@
         <v>94</v>
       </c>
       <c r="H8" s="127" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="126" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B9" s="105" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C9" s="130"/>
       <c r="D9" s="130"/>
@@ -9683,7 +9720,7 @@
         <v>9</v>
       </c>
       <c r="G9" s="127" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H9" s="127" t="s">
         <v>94</v>
@@ -9691,10 +9728,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="126" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B10" s="105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C10" s="130"/>
       <c r="D10" s="130"/>
@@ -9705,15 +9742,15 @@
         <v>94</v>
       </c>
       <c r="H10" s="127" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="126" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B11" s="105" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C11" s="130"/>
       <c r="D11" s="130"/>
@@ -9721,7 +9758,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>94</v>
@@ -9729,10 +9766,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="126" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B12" s="105" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C12" s="130"/>
       <c r="D12" s="130"/>
@@ -9743,15 +9780,15 @@
         <v>94</v>
       </c>
       <c r="H12" s="127" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="126" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B13" s="105" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C13" s="130"/>
       <c r="D13" s="130"/>
@@ -9759,7 +9796,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H13" s="127" t="s">
         <v>94</v>
@@ -9767,10 +9804,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="126" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B14" s="105" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C14" s="130"/>
       <c r="D14" s="130"/>
@@ -9778,7 +9815,7 @@
         <v>7</v>
       </c>
       <c r="G14" s="127" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H14" s="127" t="s">
         <v>94</v>
@@ -9786,10 +9823,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="126" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B15" s="105" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C15" s="130"/>
       <c r="D15" s="130"/>
@@ -9800,20 +9837,20 @@
         <v>94</v>
       </c>
       <c r="H15" s="127" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="31.75" x14ac:dyDescent="0.45">
       <c r="A16" s="159" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B16" s="160" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C16" s="130"/>
       <c r="D16" s="130"/>
       <c r="E16" s="161" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F16" s="162"/>
       <c r="G16" s="163" t="s">
@@ -9825,13 +9862,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="131" t="s">
+        <v>290</v>
+      </c>
+      <c r="B17" s="105" t="s">
+        <v>301</v>
+      </c>
+      <c r="E17" s="129" t="s">
         <v>291</v>
-      </c>
-      <c r="B17" s="105" t="s">
-        <v>302</v>
-      </c>
-      <c r="E17" s="129" t="s">
-        <v>292</v>
       </c>
       <c r="G17" s="127" t="s">
         <v>135</v>
@@ -9919,7 +9956,7 @@
         <v>141</v>
       </c>
       <c r="B4" s="133" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="113" t="s">
         <v>57</v>
@@ -9933,10 +9970,10 @@
     </row>
     <row r="5" spans="1:5" ht="26.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="166" t="s">
+        <v>336</v>
+      </c>
+      <c r="B5" s="133" t="s">
         <v>337</v>
-      </c>
-      <c r="B5" s="133" t="s">
-        <v>338</v>
       </c>
       <c r="C5" s="113" t="s">
         <v>57</v>
@@ -9950,10 +9987,10 @@
     </row>
     <row r="6" spans="1:5" ht="26.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="166" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B6" s="133" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C6" s="113" t="s">
         <v>57</v>
@@ -9967,10 +10004,10 @@
     </row>
     <row r="7" spans="1:5" ht="26.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="166" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B7" s="133" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C7" s="113" t="s">
         <v>57</v>
@@ -10212,7 +10249,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -10229,7 +10266,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -10396,7 +10433,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -10788,7 +10825,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -10805,7 +10842,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -10861,7 +10898,7 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="165" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B13" s="41" t="s">
         <v>21</v>
@@ -10875,11 +10912,11 @@
       <c r="E13" s="51"/>
       <c r="F13" s="41"/>
       <c r="G13" s="56" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H13" s="41"/>
       <c r="I13" s="41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>97</v>
@@ -10890,7 +10927,7 @@
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="165" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>53</v>
@@ -11160,7 +11197,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -11177,7 +11214,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -11305,7 +11342,7 @@
         <v>82</v>
       </c>
       <c r="K15" s="83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
@@ -11570,7 +11607,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -11587,7 +11624,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -11731,7 +11768,7 @@
         <v>22</v>
       </c>
       <c r="D16" s="146" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="29"/>
@@ -12016,7 +12053,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="61.3828125" defaultRowHeight="12.9" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.69140625" style="60" customWidth="1"/>
@@ -12237,7 +12274,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -12254,7 +12291,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -12310,7 +12347,7 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="171" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B13" s="136" t="s">
         <v>21</v>
@@ -12337,10 +12374,10 @@
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="172" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="C14" s="35" t="s">
         <v>22</v>
@@ -12349,7 +12386,7 @@
         <v>29</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>194</v>
+        <v>413</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
@@ -12358,253 +12395,24 @@
       <c r="J14" s="50" t="s">
         <v>195</v>
       </c>
-      <c r="K14" s="83" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="143" t="s">
-        <v>200</v>
-      </c>
-      <c r="B15" s="144" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="144" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="143"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="143"/>
-      <c r="I15" s="143"/>
-      <c r="J15" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="K15" s="142" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="148" t="s">
-        <v>185</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="K16" s="61" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="148" t="s">
-        <v>186</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="I17" s="41"/>
-      <c r="J17" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="K17" s="61" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="148" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="K18" s="61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="148" t="s">
-        <v>188</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="55" t="s">
-        <v>171</v>
-      </c>
-      <c r="K19" s="61" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="148" t="s">
-        <v>189</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="55" t="s">
-        <v>172</v>
-      </c>
-      <c r="K20" s="61" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="148" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="55" t="s">
-        <v>173</v>
-      </c>
-      <c r="K21" s="61" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="148" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="K22" s="61" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="17" customFormat="1" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="149"/>
-      <c r="K23" s="53"/>
-    </row>
-    <row r="24" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="71" t="s">
+      <c r="K14" s="177" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="73"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12838,7 +12646,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -12855,7 +12663,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -12911,7 +12719,7 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="165" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B13" s="41" t="s">
         <v>21</v>
@@ -12920,7 +12728,7 @@
         <v>22</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="41"/>
@@ -12928,15 +12736,15 @@
       <c r="H13" s="41"/>
       <c r="I13" s="41"/>
       <c r="J13" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="K13" s="76" t="s">
         <v>207</v>
-      </c>
-      <c r="K13" s="76" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="165" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>51</v>
@@ -12951,14 +12759,14 @@
       <c r="F14" s="51"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I14" s="26"/>
       <c r="J14" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K14" s="77" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -13205,7 +13013,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -13222,7 +13030,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -13276,7 +13084,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="173" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B13" s="40" t="s">
         <v>21</v>
@@ -13303,7 +13111,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="172" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>21</v>
@@ -13330,7 +13138,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="173" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B15" s="40" t="s">
         <v>53</v>
@@ -13346,18 +13154,18 @@
       <c r="G15" s="26"/>
       <c r="H15" s="48"/>
       <c r="I15" s="49" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J15" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="K15" s="70" t="s">
         <v>236</v>
-      </c>
-      <c r="K15" s="70" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="172" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>51</v>
@@ -13372,16 +13180,16 @@
       <c r="F16" s="34"/>
       <c r="G16" s="34"/>
       <c r="H16" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I16" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J16" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="K16" s="83" t="s">
         <v>238</v>
-      </c>
-      <c r="K16" s="83" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">

--- a/documentation/integrations/DataExchangeSpecification_v1.0.1.xlsx
+++ b/documentation/integrations/DataExchangeSpecification_v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\io\41-19-12-2025\documentation\integrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836D468B-B526-4806-81C9-7446F1F1D7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEDFCE5-7297-41AE-AE95-D9AAFB706F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="418">
   <si>
     <t>Съобщение</t>
   </si>
@@ -1307,6 +1307,9 @@
   </si>
   <si>
     <t>В съобщение E007 е коригиран формата на полето certificateNumber</t>
+  </si>
+  <si>
+    <t>В съобщение E007 полето certificateNumber става задължително</t>
   </si>
 </sst>
 </file>
@@ -3565,7 +3568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08192E09-6292-4A91-B17D-80DDC8ADAD3E}">
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3749,6 +3752,11 @@
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>416</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -13223,12 +13231,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D83CB400C3424C4590915CF6C5E758B7" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a7cb2b26aaf8d99e710797990a2b1c47">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3b615667-b975-40b1-ae5a-ef4d6726c426" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d61f9b077eef3841a59297a4bf8056c9" ns2:_="">
     <xsd:import namespace="3b615667-b975-40b1-ae5a-ef4d6726c426"/>
@@ -13366,6 +13368,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65E5A92E-C191-4A71-B1E7-50CA46998E16}">
   <ds:schemaRefs>
@@ -13375,15 +13383,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD1B6951-90F6-4939-9AC0-9F1A59AE0CAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01814C20-87D5-416B-8528-D2BB09E83DFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13399,4 +13398,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD1B6951-90F6-4939-9AC0-9F1A59AE0CAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>